--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2506-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2506-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F0DFE78-F84E-432E-A640-D3C3C48D8C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C6197A8-8D11-4543-B95F-04DF3A6A3E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{9B970A7B-84CD-40AD-A9AE-C31A9804858F}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{53B2FC87-5668-430D-BB8F-62FFAACF95AE}"/>
   </bookViews>
   <sheets>
     <sheet name="2506-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1559,30 +1559,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FCE46D-D619-470E-A858-4ED0FE5E7308}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E41D934F-7D02-4883-9D59-EB01C36E6B5E}">
   <dimension ref="A1:X59"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1616,7 +1616,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1652,7 +1652,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1772,7 +1772,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="40">
         <v>2024</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="38">
         <v>2023</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="40">
         <v>2022</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2021</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="40">
         <v>2020</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2019</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <v>2018</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2017</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="40">
         <v>2016</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2015</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
         <v>2014</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2013</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>2012</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>2011</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <v>2010</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="38">
         <v>2009</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="40">
         <v>2008</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>2007</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>2006</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>2005</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <v>2004</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38">
         <v>2003</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="40">
         <v>2002</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="38">
         <v>2001</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="40">
         <v>2000</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="38">
         <v>1999</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="40">
         <v>1998</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="38">
         <v>1997</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>7.73</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="40">
         <v>1996</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="38">
         <v>1995</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="40">
         <v>1994</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="38">
         <v>1993</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="42">
         <v>1992</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="44"/>
       <c r="B50" s="45"/>
       <c r="C50" s="21" t="s">
@@ -5062,7 +5062,7 @@
       <c r="W50" s="51"/>
       <c r="X50" s="47"/>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38">
         <v>1991</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="40">
         <v>1990</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>9.01</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="38">
         <v>1989</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="40">
         <v>1988</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="38">
         <v>1987</v>
       </c>
@@ -5422,7 +5422,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="40">
         <v>1985</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="38">
         <v>1984</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="40">
         <v>1983</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="38" t="s">
         <v>61</v>
       </c>
